--- a/docs/project-plan-progress.xlsx
+++ b/docs/project-plan-progress.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9872" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12100" uniqueCount="391">
   <si>
     <t>workstream</t>
   </si>

--- a/docs/project-plan-progress.xlsx
+++ b/docs/project-plan-progress.xlsx
@@ -19,14 +19,14 @@
     <sheet name="Progress Graph" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5762" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13061" uniqueCount="420">
   <si>
     <t>workstream</t>
   </si>
@@ -1250,6 +1250,42 @@
   </si>
   <si>
     <t>Workstream E | stand up SQLite-backed workflow state stores for project and boilerplate automation</t>
+  </si>
+  <si>
+    <t>add governance-breach notification and trust-grant logging to database-backed mechanics</t>
+  </si>
+  <si>
+    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
+  </si>
+  <si>
+    <t>2026-02-18T22:00:41Z</t>
+  </si>
+  <si>
+    <t>Workstream E | add governance-breach notification and trust-grant logging to database-backed mechanics</t>
+  </si>
+  <si>
+    <t>add database-backed file-discipline and mirrored VCS ledger reporting</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes preview/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>2026-02-18T22:09:50Z</t>
+  </si>
+  <si>
+    <t>Workstream E | add database-backed file-discipline and mirrored VCS ledger reporting</t>
+  </si>
+  <si>
+    <t>enforce hard product-management module boundaries in build quality gate</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference afp-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>2026-02-18T22:15:54Z</t>
+  </si>
+  <si>
+    <t>Workstream E | enforce hard product-management module boundaries in build quality gate</t>
   </si>
 </sst>
 </file>
@@ -2112,7 +2148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.1640625"/>
@@ -2652,8 +2688,77 @@
         <v>405</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>417</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G23" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:G26" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="3">
       <filters>
         <filter val="50"/>
@@ -2691,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -6206,6 +6311,111 @@
       </c>
       <c r="K116" t="s" s="0">
         <v>405</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>410</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F117" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="G117" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H117" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="I117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J117" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K117" t="s" s="0">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>414</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="D118" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="E118" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F118" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="G118" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H118" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="I118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J118" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K118" t="s" s="0">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>418</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="D119" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="E119" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F119" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="G119" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H119" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="I119" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J119" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K119" t="s" s="0">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -6215,7 +6425,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -9582,6 +9792,93 @@
         <v>9</v>
       </c>
       <c r="I116" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G117" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="H117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I117" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D118" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="E118" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G118" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="H118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I118" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D119" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="E119" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F119" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G119" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="H119" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I119" t="s" s="0">
         <v>243</v>
       </c>
     </row>
@@ -9592,7 +9889,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:BO83"/>
+  <dimension ref="A1:BR86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -9777,24 +10074,33 @@
         <v>361</v>
       </c>
       <c r="BI1" t="s" s="0">
+        <v>415</v>
+      </c>
+      <c r="BJ1" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="BK1" t="s" s="0">
         <v>362</v>
       </c>
-      <c r="BJ1" t="s" s="0">
+      <c r="BL1" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="BM1" t="s" s="0">
         <v>363</v>
       </c>
-      <c r="BK1" t="s" s="0">
+      <c r="BN1" t="s" s="0">
         <v>407</v>
       </c>
-      <c r="BL1" t="s" s="0">
+      <c r="BO1" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="BM1" t="s" s="0">
+      <c r="BP1" t="s" s="0">
         <v>365</v>
       </c>
-      <c r="BN1" t="s" s="0">
+      <c r="BQ1" t="s" s="0">
         <v>366</v>
       </c>
-      <c r="BO1" t="s" s="0">
+      <c r="BR1" t="s" s="0">
         <v>367</v>
       </c>
     </row>
@@ -9980,24 +10286,33 @@
         <v>74</v>
       </c>
       <c r="BI2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="BJ2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="BK2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="BJ2" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="BK2" t="s" s="0">
+      <c r="BL2" t="s" s="0">
         <v>9</v>
-      </c>
-      <c r="BL2" t="s" s="0">
-        <v>74</v>
       </c>
       <c r="BM2" t="s" s="0">
         <v>74</v>
       </c>
       <c r="BN2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="BO2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="BO2" t="s" s="0">
+      <c r="BP2" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BQ2" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BR2" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -10183,24 +10498,33 @@
         <v>9</v>
       </c>
       <c r="BI3" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BJ3" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BK3" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="BJ3" t="s" s="0">
+      <c r="BL3" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BM3" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="BK3" t="s" s="0">
-        <v>206</v>
-      </c>
-      <c r="BL3" t="s" s="0">
+      <c r="BN3" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BO3" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="BM3" t="s" s="0">
+      <c r="BP3" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="BN3" t="s" s="0">
+      <c r="BQ3" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="BO3" t="s" s="0">
+      <c r="BR3" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -10404,6 +10728,15 @@
         <v>206</v>
       </c>
       <c r="BO4" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP4" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ4" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR4" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -10607,6 +10940,15 @@
         <v>206</v>
       </c>
       <c r="BO5" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP5" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ5" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR5" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -10810,6 +11152,15 @@
         <v>206</v>
       </c>
       <c r="BO6" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP6" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ6" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR6" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11013,6 +11364,15 @@
         <v>206</v>
       </c>
       <c r="BO7" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP7" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ7" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR7" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11216,6 +11576,15 @@
         <v>206</v>
       </c>
       <c r="BO8" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP8" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ8" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR8" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11419,6 +11788,15 @@
         <v>206</v>
       </c>
       <c r="BO9" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP9" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ9" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR9" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11622,6 +12000,15 @@
         <v>206</v>
       </c>
       <c r="BO10" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP10" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ10" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR10" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11825,6 +12212,15 @@
         <v>206</v>
       </c>
       <c r="BO11" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP11" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ11" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR11" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -12028,6 +12424,15 @@
         <v>206</v>
       </c>
       <c r="BO12" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP12" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ12" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR12" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -12231,6 +12636,15 @@
         <v>206</v>
       </c>
       <c r="BO13" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP13" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ13" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR13" t="s" s="0">
         <v>32</v>
       </c>
     </row>
@@ -12434,6 +12848,15 @@
         <v>206</v>
       </c>
       <c r="BO14" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP14" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ14" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR14" t="s" s="0">
         <v>96</v>
       </c>
     </row>
@@ -13099,65 +13522,65 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>362</v>
+        <v>415</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C82" t="s" s="0">
         <v>9</v>
@@ -13165,12 +13588,45 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
         <v>367</v>
       </c>
-      <c r="B83" t="s" s="0">
+      <c r="B86" t="s" s="0">
         <v>375</v>
       </c>
-      <c r="C83" t="s" s="0">
+      <c r="C86" t="s" s="0">
         <v>96</v>
       </c>
     </row>

--- a/docs/project-plan-progress.xlsx
+++ b/docs/project-plan-progress.xlsx
@@ -19,14 +19,14 @@
     <sheet name="Progress Graph" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13061" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23522" uniqueCount="460">
   <si>
     <t>workstream</t>
   </si>
@@ -1286,6 +1286,126 @@
   </si>
   <si>
     <t>Workstream E | enforce hard product-management module boundaries in build quality gate</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed).</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior.</t>
+  </si>
+  <si>
+    <t>2026-02-18T22:24:39Z</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,0,0,96,97,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        @@@</t>
+  </si>
+  <si>
+    <t>0,95,97</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @@</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,0,0,0,0,0,90,91,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           %%%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              </t>
+  </si>
+  <si>
+    <t>@@@@@@@@@@@@@@</t>
+  </si>
+  <si>
+    <t>++++++++++++++</t>
+  </si>
+  <si>
+    <t>--------------</t>
+  </si>
+  <si>
+    <t>::::::::::::::</t>
+  </si>
+  <si>
+    <t>==============</t>
+  </si>
+  <si>
+    <t>@*************</t>
+  </si>
+  <si>
+    <t>..............</t>
+  </si>
+  <si>
+    <t>##############</t>
+  </si>
+  <si>
+    <t>%%%%%%%%%%%%%%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> *************</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        @@@@@@</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @@@@@@@@@@@@@</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> #############</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> %%%%%%%%%%%%%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   @@@@@@@@@@@</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      %%%%%%%%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +++++++++++++</t>
+  </si>
+  <si>
+    <t>enforce managed-tooling registration discipline in build quality gate</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `afp-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>2026-02-18T22:38:09Z</t>
+  </si>
+  <si>
+    <t>Workstream E | enforce managed-tooling registration discipline in build quality gate</t>
+  </si>
+  <si>
+    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>2026-02-18T22:51:27Z</t>
+  </si>
+  <si>
+    <t>100,100</t>
+  </si>
+  <si>
+    <t>@@</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>2026-02-18T23:13:58Z</t>
   </si>
 </sst>
 </file>
@@ -2148,7 +2268,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.1640625"/>
@@ -2265,13 +2385,13 @@
         <v>15</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>369</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6">
@@ -2633,13 +2753,13 @@
         <v>15</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>63</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22">
@@ -2656,13 +2776,13 @@
         <v>15</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>370</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23">
@@ -2685,7 +2805,7 @@
         <v>10</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>405</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24">
@@ -2731,7 +2851,7 @@
         <v>10</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>413</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26">
@@ -2754,11 +2874,34 @@
         <v>10</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>417</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>454</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G26" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:G27" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="3">
       <filters>
         <filter val="50"/>
@@ -2796,7 +2939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -6416,6 +6559,286 @@
       </c>
       <c r="K119" t="s" s="0">
         <v>417</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D120" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E120" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F120" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="G120" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H120" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="I120" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J120" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K120" t="s" s="0">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D121" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F121" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="G121" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H121" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="I121" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="J121" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K121" t="s" s="0">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D122" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E122" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F122" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="G122" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H122" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="I122" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="J122" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K122" t="s" s="0">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="D123" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="E123" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F123" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="G123" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H123" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="I123" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J123" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K123" t="s" s="0">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>455</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D124" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E124" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F124" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="G124" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J124" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K124" t="s" s="0">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>455</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F125" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="G125" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J125" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K125" t="s" s="0">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>455</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="D126" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E126" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F126" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="G126" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H126" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I126" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J126" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K126" t="s" s="0">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>459</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="D127" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E127" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="F127" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="G127" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="H127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="J127" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="K127" t="s" s="0">
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -6425,7 +6848,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -9880,6 +10303,238 @@
       </c>
       <c r="I119" t="s" s="0">
         <v>243</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D120" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="E120" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F120" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="G120" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="H120" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="I120" t="s" s="0">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D121" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F121" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="G121" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="H121" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="I121" t="s" s="0">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D122" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="E122" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F122" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G122" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="H122" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="I122" t="s" s="0">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D123" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="E123" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F123" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G123" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="H123" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="I123" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D124" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E124" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G124" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="H124" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="I124" t="s" s="0">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G125" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="H125" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="I125" t="s" s="0">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D126" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E126" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F126" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G126" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="H126" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="I126" t="s" s="0">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="D127" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E127" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G127" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="H127" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="I127" t="s" s="0">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -9889,7 +10544,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:BR86"/>
+  <dimension ref="A1:BS88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -10086,21 +10741,24 @@
         <v>419</v>
       </c>
       <c r="BM1" t="s" s="0">
+        <v>451</v>
+      </c>
+      <c r="BN1" t="s" s="0">
         <v>363</v>
       </c>
-      <c r="BN1" t="s" s="0">
+      <c r="BO1" t="s" s="0">
         <v>407</v>
       </c>
-      <c r="BO1" t="s" s="0">
+      <c r="BP1" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="BP1" t="s" s="0">
+      <c r="BQ1" t="s" s="0">
         <v>365</v>
       </c>
-      <c r="BQ1" t="s" s="0">
+      <c r="BR1" t="s" s="0">
         <v>366</v>
       </c>
-      <c r="BR1" t="s" s="0">
+      <c r="BS1" t="s" s="0">
         <v>367</v>
       </c>
     </row>
@@ -10298,13 +10956,13 @@
         <v>9</v>
       </c>
       <c r="BM2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="BN2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="BN2" t="s" s="0">
+      <c r="BO2" t="s" s="0">
         <v>9</v>
-      </c>
-      <c r="BO2" t="s" s="0">
-        <v>74</v>
       </c>
       <c r="BP2" t="s" s="0">
         <v>74</v>
@@ -10313,6 +10971,9 @@
         <v>74</v>
       </c>
       <c r="BR2" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BS2" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -10498,7 +11159,7 @@
         <v>9</v>
       </c>
       <c r="BI3" t="s" s="0">
-        <v>206</v>
+        <v>9</v>
       </c>
       <c r="BJ3" t="s" s="0">
         <v>206</v>
@@ -10507,24 +11168,27 @@
         <v>50</v>
       </c>
       <c r="BL3" t="s" s="0">
-        <v>206</v>
+        <v>9</v>
       </c>
       <c r="BM3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="BN3" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="BN3" t="s" s="0">
-        <v>206</v>
-      </c>
       <c r="BO3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="BP3" t="s" s="0">
         <v>62</v>
-      </c>
-      <c r="BP3" t="s" s="0">
-        <v>9</v>
       </c>
       <c r="BQ3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="BR3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="BS3" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -10731,12 +11395,15 @@
         <v>206</v>
       </c>
       <c r="BP4" t="s" s="0">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="BQ4" t="s" s="0">
         <v>206</v>
       </c>
       <c r="BR4" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS4" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -10949,6 +11616,9 @@
         <v>206</v>
       </c>
       <c r="BR5" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS5" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11161,6 +11831,9 @@
         <v>206</v>
       </c>
       <c r="BR6" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS6" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11373,6 +12046,9 @@
         <v>206</v>
       </c>
       <c r="BR7" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS7" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11585,6 +12261,9 @@
         <v>206</v>
       </c>
       <c r="BR8" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS8" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -11797,6 +12476,9 @@
         <v>206</v>
       </c>
       <c r="BR9" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS9" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -12009,6 +12691,9 @@
         <v>206</v>
       </c>
       <c r="BR10" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS10" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -12221,6 +12906,9 @@
         <v>206</v>
       </c>
       <c r="BR11" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS11" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -12364,7 +13052,7 @@
         <v>206</v>
       </c>
       <c r="AU12" t="s" s="0">
-        <v>206</v>
+        <v>102</v>
       </c>
       <c r="AV12" t="s" s="0">
         <v>206</v>
@@ -12433,6 +13121,9 @@
         <v>206</v>
       </c>
       <c r="BR12" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS12" t="s" s="0">
         <v>74</v>
       </c>
     </row>
@@ -12645,6 +13336,9 @@
         <v>206</v>
       </c>
       <c r="BR13" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS13" t="s" s="0">
         <v>32</v>
       </c>
     </row>
@@ -12857,543 +13551,750 @@
         <v>206</v>
       </c>
       <c r="BR14" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS14" t="s" s="0">
         <v>96</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>238</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>368</v>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="I15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="K15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="L15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="P15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="Q15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="R15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="S15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="T15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="U15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="V15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="W15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="X15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="Y15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="Z15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AA15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AB15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AC15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AD15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AE15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AF15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AG15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AH15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AI15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AJ15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AK15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AL15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AM15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AN15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AO15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AP15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AQ15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AR15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AS15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AT15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AU15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AV15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AW15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AX15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AY15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="AZ15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BA15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BB15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BC15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BD15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BE15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BF15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BG15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BH15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BI15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BJ15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BK15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BL15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BM15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BN15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BO15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BP15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BQ15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BR15" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="BS15" t="s" s="0">
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>303</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>376</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>80</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>116</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>378</v>
+        <v>431</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>65</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>377</v>
+        <v>432</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>140</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>379</v>
+        <v>431</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>380</v>
+        <v>433</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>380</v>
+        <v>434</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>379</v>
+        <v>433</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>379</v>
+        <v>433</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>379</v>
+        <v>433</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>381</v>
+        <v>433</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>50</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>203</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>153</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>380</v>
+        <v>434</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="C53" t="s" s="0">
-        <v>26</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>94</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>32</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>99</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>377</v>
+        <v>439</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>16</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="C65" t="s" s="0">
         <v>9</v>
@@ -13401,98 +14302,98 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>389</v>
+        <v>443</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>391</v>
+        <v>443</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>389</v>
+        <v>445</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>388</v>
+        <v>443</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="C74" t="s" s="0">
         <v>9</v>
@@ -13500,32 +14401,32 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>99</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>415</v>
+        <v>361</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="C77" t="s" s="0">
         <v>9</v>
@@ -13533,10 +14434,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C78" t="s" s="0">
         <v>9</v>
@@ -13544,43 +14445,43 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>419</v>
+        <v>362</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>377</v>
+        <v>447</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="C82" t="s" s="0">
         <v>9</v>
@@ -13588,21 +14489,21 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>62</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="C84" t="s" s="0">
         <v>9</v>
@@ -13610,24 +14511,46 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>9</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>442</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>442</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
         <v>367</v>
       </c>
-      <c r="B86" t="s" s="0">
-        <v>375</v>
-      </c>
-      <c r="C86" t="s" s="0">
-        <v>96</v>
+      <c r="B88" t="s" s="0">
+        <v>429</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/docs/project-plan-progress.xlsx
+++ b/docs/project-plan-progress.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="177">
   <si>
     <t>workstream</t>
   </si>
@@ -488,6 +488,66 @@
   </si>
   <si>
     <t>latest_percent</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>2026-02-19T18:56:27Z</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>98,100</t>
+  </si>
+  <si>
+    <t>@@</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>90,100</t>
+  </si>
+  <si>
+    <t>%@</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>94,100</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>97,100</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>++</t>
+  </si>
+  <si>
+    <t>%%</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
 </sst>
 </file>
@@ -637,16 +697,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>22</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
@@ -729,16 +789,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>35</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -867,16 +927,16 @@
         <v>38</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>51</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16">
@@ -1005,16 +1065,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>67</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
@@ -1346,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
@@ -2571,6 +2631,146 @@
       </c>
       <c r="K35" t="s" s="0">
         <v>99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K36" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="I37" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K37" t="s" s="0">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="I38" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J38" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K38" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="I39" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J39" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="K39" t="s" s="0">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:dimension ref="A1:J35"/>
+  <ns0:dimension ref="A1:J39"/>
   <ns0:sheetData>
     <ns0:row r="1">
       <ns0:c r="A1" t="s" s="0">
@@ -3597,6 +3797,122 @@
       </ns0:c>
       <ns0:c r="I35" t="s" s="0">
         <ns0:v>117</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="36">
+      <ns0:c r="A36" t="s" s="0">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B36" t="s" s="0">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="C36" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D36" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E36" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F36" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G36" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="H36" t="s" s="0">
+        <ns0:v>163</ns0:v>
+      </ns0:c>
+      <ns0:c r="I36" t="s" s="0">
+        <ns0:v>164</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="37">
+      <ns0:c r="A37" t="s" s="0">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="B37" t="s" s="0">
+        <ns0:v>33</ns0:v>
+      </ns0:c>
+      <ns0:c r="C37" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D37" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E37" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F37" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G37" t="s" s="0">
+        <ns0:v>165</ns0:v>
+      </ns0:c>
+      <ns0:c r="H37" t="s" s="0">
+        <ns0:v>166</ns0:v>
+      </ns0:c>
+      <ns0:c r="I37" t="s" s="0">
+        <ns0:v>167</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="38">
+      <ns0:c r="A38" t="s" s="0">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="B38" t="s" s="0">
+        <ns0:v>49</ns0:v>
+      </ns0:c>
+      <ns0:c r="C38" t="s" s="0">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="D38" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E38" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F38" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G38" t="s" s="0">
+        <ns0:v>168</ns0:v>
+      </ns0:c>
+      <ns0:c r="H38" t="s" s="0">
+        <ns0:v>169</ns0:v>
+      </ns0:c>
+      <ns0:c r="I38" t="s" s="0">
+        <ns0:v>167</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="39">
+      <ns0:c r="A39" t="s" s="0">
+        <ns0:v>60</ns0:v>
+      </ns0:c>
+      <ns0:c r="B39" t="s" s="0">
+        <ns0:v>65</ns0:v>
+      </ns0:c>
+      <ns0:c r="C39" t="s" s="0">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D39" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="E39" t="s" s="0">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="F39" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="G39" t="s" s="0">
+        <ns0:v>170</ns0:v>
+      </ns0:c>
+      <ns0:c r="H39" t="s" s="0">
+        <ns0:v>171</ns0:v>
+      </ns0:c>
+      <ns0:c r="I39" t="s" s="0">
+        <ns0:v>164</ns0:v>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
@@ -3605,7 +3921,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:dimension ref="A1:AI39"/>
+  <ns0:dimension ref="A1:AI40"/>
   <ns0:sheetData>
     <ns0:row r="1">
       <ns0:c r="A1" t="s" s="0">
@@ -3821,45 +4137,141 @@
         <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" t="s" s="0">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="B5" t="s" s="0">
-        <ns0:v>113</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" t="s" s="0">
-        <ns0:v>156</ns0:v>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="s" s="0">
+        <ns0:v>162</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="L3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="M3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="N3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="O3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="P3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="Q3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="R3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="S3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="T3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="U3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="V3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="W3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="X3" t="s" s="0">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AB3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AC3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AD3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH3" t="s" s="0">
+        <ns0:v>109</ns0:v>
+      </ns0:c>
+      <ns0:c r="AI3" t="s" s="0">
+        <ns0:v>109</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6">
       <ns0:c r="A6" t="s" s="0">
-        <ns0:v>122</ns0:v>
+        <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="B6" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>113</ns0:v>
       </ns0:c>
       <ns0:c r="C6" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>156</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="7">
       <ns0:c r="A7" t="s" s="0">
-        <ns0:v>123</ns0:v>
+        <ns0:v>122</ns0:v>
       </ns0:c>
       <ns0:c r="B7" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C7" t="s" s="0">
-        <ns0:v>21</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="8">
       <ns0:c r="A8" t="s" s="0">
-        <ns0:v>124</ns0:v>
+        <ns0:v>123</ns0:v>
       </ns0:c>
       <ns0:c r="B8" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C8" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3867,10 +4279,10 @@
     </ns0:row>
     <ns0:row r="9">
       <ns0:c r="A9" t="s" s="0">
-        <ns0:v>125</ns0:v>
+        <ns0:v>124</ns0:v>
       </ns0:c>
       <ns0:c r="B9" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C9" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3878,98 +4290,98 @@
     </ns0:row>
     <ns0:row r="10">
       <ns0:c r="A10" t="s" s="0">
-        <ns0:v>126</ns0:v>
+        <ns0:v>125</ns0:v>
       </ns0:c>
       <ns0:c r="B10" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C10" t="s" s="0">
-        <ns0:v>28</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="11">
       <ns0:c r="A11" t="s" s="0">
-        <ns0:v>127</ns0:v>
+        <ns0:v>126</ns0:v>
       </ns0:c>
       <ns0:c r="B11" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C11" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>28</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="12">
       <ns0:c r="A12" t="s" s="0">
-        <ns0:v>128</ns0:v>
+        <ns0:v>127</ns0:v>
       </ns0:c>
       <ns0:c r="B12" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C12" t="s" s="0">
-        <ns0:v>31</ns0:v>
+        <ns0:v>25</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="13">
       <ns0:c r="A13" t="s" s="0">
-        <ns0:v>129</ns0:v>
+        <ns0:v>128</ns0:v>
       </ns0:c>
       <ns0:c r="B13" t="s" s="0">
-        <ns0:v>119</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C13" t="s" s="0">
-        <ns0:v>34</ns0:v>
+        <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="14">
       <ns0:c r="A14" t="s" s="0">
-        <ns0:v>130</ns0:v>
+        <ns0:v>129</ns0:v>
       </ns0:c>
       <ns0:c r="B14" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>167</ns0:v>
       </ns0:c>
       <ns0:c r="C14" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="15">
       <ns0:c r="A15" t="s" s="0">
-        <ns0:v>131</ns0:v>
+        <ns0:v>130</ns0:v>
       </ns0:c>
       <ns0:c r="B15" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C15" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>25</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="16">
       <ns0:c r="A16" t="s" s="0">
-        <ns0:v>132</ns0:v>
+        <ns0:v>131</ns0:v>
       </ns0:c>
       <ns0:c r="B16" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C16" t="s" s="0">
-        <ns0:v>28</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="17">
       <ns0:c r="A17" t="s" s="0">
-        <ns0:v>133</ns0:v>
+        <ns0:v>132</ns0:v>
       </ns0:c>
       <ns0:c r="B17" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>173</ns0:v>
       </ns0:c>
       <ns0:c r="C17" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>28</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="18">
       <ns0:c r="A18" t="s" s="0">
-        <ns0:v>134</ns0:v>
+        <ns0:v>133</ns0:v>
       </ns0:c>
       <ns0:c r="B18" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C18" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3977,21 +4389,21 @@
     </ns0:row>
     <ns0:row r="19">
       <ns0:c r="A19" t="s" s="0">
-        <ns0:v>135</ns0:v>
+        <ns0:v>134</ns0:v>
       </ns0:c>
       <ns0:c r="B19" t="s" s="0">
-        <ns0:v>119</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C19" t="s" s="0">
-        <ns0:v>50</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="20">
       <ns0:c r="A20" t="s" s="0">
-        <ns0:v>136</ns0:v>
+        <ns0:v>135</ns0:v>
       </ns0:c>
       <ns0:c r="B20" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>167</ns0:v>
       </ns0:c>
       <ns0:c r="C20" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -3999,10 +4411,10 @@
     </ns0:row>
     <ns0:row r="21">
       <ns0:c r="A21" t="s" s="0">
-        <ns0:v>137</ns0:v>
+        <ns0:v>136</ns0:v>
       </ns0:c>
       <ns0:c r="B21" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C21" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4010,10 +4422,10 @@
     </ns0:row>
     <ns0:row r="22">
       <ns0:c r="A22" t="s" s="0">
-        <ns0:v>138</ns0:v>
+        <ns0:v>137</ns0:v>
       </ns0:c>
       <ns0:c r="B22" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C22" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4021,32 +4433,32 @@
     </ns0:row>
     <ns0:row r="23">
       <ns0:c r="A23" t="s" s="0">
-        <ns0:v>139</ns0:v>
+        <ns0:v>138</ns0:v>
       </ns0:c>
       <ns0:c r="B23" t="s" s="0">
-        <ns0:v>120</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C23" t="s" s="0">
-        <ns0:v>54</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="24">
       <ns0:c r="A24" t="s" s="0">
-        <ns0:v>140</ns0:v>
+        <ns0:v>139</ns0:v>
       </ns0:c>
       <ns0:c r="B24" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>174</ns0:v>
       </ns0:c>
       <ns0:c r="C24" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>54</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="25">
       <ns0:c r="A25" t="s" s="0">
-        <ns0:v>141</ns0:v>
+        <ns0:v>140</ns0:v>
       </ns0:c>
       <ns0:c r="B25" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C25" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4054,43 +4466,43 @@
     </ns0:row>
     <ns0:row r="26">
       <ns0:c r="A26" t="s" s="0">
-        <ns0:v>142</ns0:v>
+        <ns0:v>141</ns0:v>
       </ns0:c>
       <ns0:c r="B26" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C26" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="27">
       <ns0:c r="A27" t="s" s="0">
-        <ns0:v>143</ns0:v>
+        <ns0:v>142</ns0:v>
       </ns0:c>
       <ns0:c r="B27" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C27" t="s" s="0">
-        <ns0:v>11</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="28">
       <ns0:c r="A28" t="s" s="0">
-        <ns0:v>144</ns0:v>
+        <ns0:v>143</ns0:v>
       </ns0:c>
       <ns0:c r="B28" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C28" t="s" s="0">
-        <ns0:v>66</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="29">
       <ns0:c r="A29" t="s" s="0">
-        <ns0:v>145</ns0:v>
+        <ns0:v>144</ns0:v>
       </ns0:c>
       <ns0:c r="B29" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C29" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4098,10 +4510,10 @@
     </ns0:row>
     <ns0:row r="30">
       <ns0:c r="A30" t="s" s="0">
-        <ns0:v>146</ns0:v>
+        <ns0:v>145</ns0:v>
       </ns0:c>
       <ns0:c r="B30" t="s" s="0">
-        <ns0:v>116</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C30" t="s" s="0">
         <ns0:v>11</ns0:v>
@@ -4109,76 +4521,76 @@
     </ns0:row>
     <ns0:row r="31">
       <ns0:c r="A31" t="s" s="0">
-        <ns0:v>147</ns0:v>
+        <ns0:v>146</ns0:v>
       </ns0:c>
       <ns0:c r="B31" t="s" s="0">
-        <ns0:v>119</ns0:v>
+        <ns0:v>164</ns0:v>
       </ns0:c>
       <ns0:c r="C31" t="s" s="0">
-        <ns0:v>69</ns0:v>
+        <ns0:v>11</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="32">
       <ns0:c r="A32" t="s" s="0">
-        <ns0:v>148</ns0:v>
+        <ns0:v>147</ns0:v>
       </ns0:c>
       <ns0:c r="B32" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>175</ns0:v>
       </ns0:c>
       <ns0:c r="C32" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>69</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="33">
       <ns0:c r="A33" t="s" s="0">
-        <ns0:v>149</ns0:v>
+        <ns0:v>148</ns0:v>
       </ns0:c>
       <ns0:c r="B33" t="s" s="0">
-        <ns0:v>120</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C33" t="s" s="0">
-        <ns0:v>54</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="34">
       <ns0:c r="A34" t="s" s="0">
-        <ns0:v>150</ns0:v>
+        <ns0:v>149</ns0:v>
       </ns0:c>
       <ns0:c r="B34" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>174</ns0:v>
       </ns0:c>
       <ns0:c r="C34" t="s" s="0">
-        <ns0:v>31</ns0:v>
+        <ns0:v>54</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="35">
       <ns0:c r="A35" t="s" s="0">
-        <ns0:v>151</ns0:v>
+        <ns0:v>150</ns0:v>
       </ns0:c>
       <ns0:c r="B35" t="s" s="0">
-        <ns0:v>121</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C35" t="s" s="0">
-        <ns0:v>90</ns0:v>
+        <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="36">
       <ns0:c r="A36" t="s" s="0">
-        <ns0:v>152</ns0:v>
+        <ns0:v>151</ns0:v>
       </ns0:c>
       <ns0:c r="B36" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>176</ns0:v>
       </ns0:c>
       <ns0:c r="C36" t="s" s="0">
-        <ns0:v>18</ns0:v>
+        <ns0:v>90</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="37">
       <ns0:c r="A37" t="s" s="0">
-        <ns0:v>153</ns0:v>
+        <ns0:v>152</ns0:v>
       </ns0:c>
       <ns0:c r="B37" t="s" s="0">
-        <ns0:v>117</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C37" t="s" s="0">
         <ns0:v>18</ns0:v>
@@ -4186,23 +4598,34 @@
     </ns0:row>
     <ns0:row r="38">
       <ns0:c r="A38" t="s" s="0">
-        <ns0:v>154</ns0:v>
+        <ns0:v>153</ns0:v>
       </ns0:c>
       <ns0:c r="B38" t="s" s="0">
-        <ns0:v>118</ns0:v>
+        <ns0:v>172</ns0:v>
       </ns0:c>
       <ns0:c r="C38" t="s" s="0">
-        <ns0:v>25</ns0:v>
+        <ns0:v>18</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="39">
       <ns0:c r="A39" t="s" s="0">
+        <ns0:v>154</ns0:v>
+      </ns0:c>
+      <ns0:c r="B39" t="s" s="0">
+        <ns0:v>173</ns0:v>
+      </ns0:c>
+      <ns0:c r="C39" t="s" s="0">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="40">
+      <ns0:c r="A40" t="s" s="0">
         <ns0:v>155</ns0:v>
       </ns0:c>
-      <ns0:c r="B39" t="s" s="0">
-        <ns0:v>117</ns0:v>
-      </ns0:c>
-      <ns0:c r="C39" t="s" s="0">
+      <ns0:c r="B40" t="s" s="0">
+        <ns0:v>172</ns0:v>
+      </ns0:c>
+      <ns0:c r="C40" t="s" s="0">
         <ns0:v>31</ns0:v>
       </ns0:c>
     </ns0:row>

--- a/docs/project-plan-progress.xlsx
+++ b/docs/project-plan-progress.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="177">
   <si>
     <t>workstream</t>
   </si>

--- a/docs/project-plan-progress.xlsx
+++ b/docs/project-plan-progress.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="177">
   <si>
     <t>workstream</t>
   </si>
